--- a/data/trans_orig/P36BPD07_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de bebidas carbonatadas y/o azucaradas que consume al día en 2023</t>
+          <t>Población según el número de bebidas carbonatadas y/o azucaradas que consume al día en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98953</t>
+          <t>101445</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165740</t>
+          <t>166611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90160</t>
+          <t>90165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133746</t>
+          <t>136039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209382</t>
+          <t>205204</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>285351</t>
+          <t>284569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>234247</t>
+          <t>233376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301034</t>
+          <t>298542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179454</t>
+          <t>177161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223040</t>
+          <t>223035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>427836</t>
+          <t>428618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>503805</t>
+          <t>507983</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132010</t>
+          <t>132486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>181913</t>
+          <t>185347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67440</t>
+          <t>65465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138160</t>
+          <t>136415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204557</t>
+          <t>200152</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>306443</t>
+          <t>307836</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>241634</t>
+          <t>238200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>291537</t>
+          <t>291061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372347</t>
+          <t>374092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>443067</t>
+          <t>445042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>627611</t>
+          <t>626218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>729497</t>
+          <t>733902</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134470</t>
+          <t>135376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180929</t>
+          <t>177453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132899</t>
+          <t>131885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166996</t>
+          <t>166282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280194</t>
+          <t>280241</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>334545</t>
+          <t>335311</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>354313</t>
+          <t>357789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>400772</t>
+          <t>399866</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>374424</t>
+          <t>375138</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>408521</t>
+          <t>409535</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>742117</t>
+          <t>741351</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>796468</t>
+          <t>796421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83203</t>
+          <t>74199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268344</t>
+          <t>265341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132426</t>
+          <t>129056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176873</t>
+          <t>176262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>196654</t>
+          <t>217557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>415634</t>
+          <t>415830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>619442</t>
+          <t>622445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>804583</t>
+          <t>813587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>534944</t>
+          <t>535555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>579391</t>
+          <t>582761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1183970</t>
+          <t>1183774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1402950</t>
+          <t>1382047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120796</t>
+          <t>122218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>159042</t>
+          <t>160041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96581</t>
+          <t>95262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124869</t>
+          <t>123845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>225436</t>
+          <t>225483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273591</t>
+          <t>272770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>399365</t>
+          <t>398366</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>437611</t>
+          <t>436189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>421997</t>
+          <t>423021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>450285</t>
+          <t>451604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>831683</t>
+          <t>832504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>879838</t>
+          <t>879791</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62153</t>
+          <t>61895</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87340</t>
+          <t>86916</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>26716</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>105961</t>
+          <t>106959</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72893</t>
+          <t>71455</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184526</t>
+          <t>184199</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279906</t>
+          <t>280330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>305093</t>
+          <t>305351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>501240</t>
+          <t>500242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>583106</t>
+          <t>580485</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>789922</t>
+          <t>790249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>901555</t>
+          <t>902993</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>49000</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68864</t>
+          <t>69179</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53714</t>
+          <t>54427</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74306</t>
+          <t>76265</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109370</t>
+          <t>108462</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137150</t>
+          <t>137742</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>213895</t>
+          <t>213580</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>235453</t>
+          <t>233759</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>350977</t>
+          <t>349018</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>371569</t>
+          <t>370856</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>570893</t>
+          <t>570301</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>598673</t>
+          <t>599581</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>709792</t>
+          <t>698607</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>995730</t>
+          <t>992630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>630700</t>
+          <t>636025</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>837814</t>
+          <t>843235</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,17 +3196,17 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1672793</t>
+          <t>1672794</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1444774</t>
+          <t>1456891</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1804471</t>
+          <t>1803512</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2459246</t>
+          <t>2462346</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2745184</t>
+          <t>2756369</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2818481</t>
+          <t>2813060</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3025595</t>
+          <t>3020270</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5306799</t>
+          <t>5307759</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5666496</t>
+          <t>5654380</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7111270</t>
+          <t>7111271</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7111270</t>
+          <t>7111271</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7111270</t>
+          <t>7111271</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P36BPD07_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>144329</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101445</t>
+          <t>116017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166611</t>
+          <t>172890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>111019</t>
+          <t>136368</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90165</t>
+          <t>112382</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136039</t>
+          <t>161805</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>243455</t>
+          <t>280697</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205204</t>
+          <t>239968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>284569</t>
+          <t>317709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>267552</t>
+          <t>263464</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>233376</t>
+          <t>234903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>298542</t>
+          <t>291776</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>202181</t>
+          <t>226144</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177161</t>
+          <t>200707</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223035</t>
+          <t>250130</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>469732</t>
+          <t>489608</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>428618</t>
+          <t>452596</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>507983</t>
+          <t>530337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>157093</t>
+          <t>170527</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132486</t>
+          <t>144682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185347</t>
+          <t>197741</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>111457</t>
+          <t>128892</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65465</t>
+          <t>108780</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136415</t>
+          <t>149259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>268550</t>
+          <t>299419</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>200152</t>
+          <t>266243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>307836</t>
+          <t>334252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>266454</t>
+          <t>306363</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238200</t>
+          <t>279149</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>291061</t>
+          <t>332208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>399050</t>
+          <t>371245</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>374092</t>
+          <t>350878</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445042</t>
+          <t>391357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>665504</t>
+          <t>677608</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>626218</t>
+          <t>642775</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733902</t>
+          <t>710784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510507</t>
+          <t>500137</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510507</t>
+          <t>500137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510507</t>
+          <t>500137</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934054</t>
+          <t>977027</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934054</t>
+          <t>977027</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934054</t>
+          <t>977027</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>156819</t>
+          <t>188872</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135376</t>
+          <t>163491</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177453</t>
+          <t>213582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>149309</t>
+          <t>171719</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131885</t>
+          <t>153093</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166282</t>
+          <t>191408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>306128</t>
+          <t>360592</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280241</t>
+          <t>330867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>335311</t>
+          <t>391715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>378423</t>
+          <t>430766</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>357789</t>
+          <t>406056</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>399866</t>
+          <t>456147</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>392111</t>
+          <t>448142</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>375138</t>
+          <t>428453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>409535</t>
+          <t>466768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>770534</t>
+          <t>878907</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>741351</t>
+          <t>847784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>796421</t>
+          <t>908632</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,31%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535242</t>
+          <t>619638</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535242</t>
+          <t>619638</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535242</t>
+          <t>619638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541420</t>
+          <t>619861</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541420</t>
+          <t>619861</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541420</t>
+          <t>619861</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076662</t>
+          <t>1239499</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076662</t>
+          <t>1239499</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076662</t>
+          <t>1239499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>184133</t>
+          <t>203551</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74199</t>
+          <t>180508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265341</t>
+          <t>231725</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>157367</t>
+          <t>178531</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129056</t>
+          <t>160762</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176262</t>
+          <t>197302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>341501</t>
+          <t>382082</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>217557</t>
+          <t>348873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>415830</t>
+          <t>412602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>703653</t>
+          <t>497066</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>622445</t>
+          <t>468892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>813587</t>
+          <t>520109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>554450</t>
+          <t>557281</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>535555</t>
+          <t>538510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>582761</t>
+          <t>575050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1258103</t>
+          <t>1054348</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1183774</t>
+          <t>1023828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1382047</t>
+          <t>1087557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711817</t>
+          <t>735812</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711817</t>
+          <t>735812</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711817</t>
+          <t>735812</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599604</t>
+          <t>1436430</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599604</t>
+          <t>1436430</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599604</t>
+          <t>1436430</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>139804</t>
+          <t>152984</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122218</t>
+          <t>133572</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160041</t>
+          <t>173419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>109488</t>
+          <t>121768</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95262</t>
+          <t>107065</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123845</t>
+          <t>137598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>249292</t>
+          <t>274752</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>225483</t>
+          <t>252031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272770</t>
+          <t>302359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>418603</t>
+          <t>453479</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>398366</t>
+          <t>433044</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>436189</t>
+          <t>472891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>437378</t>
+          <t>485982</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>423021</t>
+          <t>470152</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>451604</t>
+          <t>500685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>855982</t>
+          <t>939462</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>832504</t>
+          <t>911855</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>879791</t>
+          <t>962183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,24%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>558407</t>
+          <t>606463</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558407</t>
+          <t>606463</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558407</t>
+          <t>606463</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>546866</t>
+          <t>607750</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>546866</t>
+          <t>607750</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>546866</t>
+          <t>607750</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105274</t>
+          <t>1214214</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105274</t>
+          <t>1214214</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105274</t>
+          <t>1214214</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74105</t>
+          <t>81374</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61895</t>
+          <t>68857</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86916</t>
+          <t>96155</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>67312</t>
+          <t>74552</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>62948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106959</t>
+          <t>86555</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>141417</t>
+          <t>155926</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71455</t>
+          <t>140150</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184199</t>
+          <t>174919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>293141</t>
+          <t>324633</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280330</t>
+          <t>309852</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>305351</t>
+          <t>337150</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>539889</t>
+          <t>363354</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>500242</t>
+          <t>351351</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>580485</t>
+          <t>374958</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>833031</t>
+          <t>687987</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>790249</t>
+          <t>668994</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>902993</t>
+          <t>703763</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367246</t>
+          <t>406007</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367246</t>
+          <t>406007</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367246</t>
+          <t>406007</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607201</t>
+          <t>437906</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607201</t>
+          <t>437906</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607201</t>
+          <t>437906</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974448</t>
+          <t>843913</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974448</t>
+          <t>843913</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974448</t>
+          <t>843913</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>58410</t>
+          <t>64966</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>53279</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69179</t>
+          <t>77983</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>64041</t>
+          <t>71727</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54427</t>
+          <t>61228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76265</t>
+          <t>82683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>122451</t>
+          <t>136693</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108462</t>
+          <t>121796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137742</t>
+          <t>151692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>224349</t>
+          <t>245232</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>213580</t>
+          <t>232215</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>233759</t>
+          <t>256919</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>361242</t>
+          <t>392272</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>349018</t>
+          <t>381316</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>370856</t>
+          <t>402771</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>585592</t>
+          <t>637504</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>570301</t>
+          <t>622505</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>599581</t>
+          <t>652401</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425283</t>
+          <t>463999</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425283</t>
+          <t>463999</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425283</t>
+          <t>463999</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708043</t>
+          <t>774197</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708043</t>
+          <t>774197</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708043</t>
+          <t>774197</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>902799</t>
+          <t>1006603</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>698607</t>
+          <t>943775</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>992630</t>
+          <t>1067488</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>769995</t>
+          <t>883558</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>636025</t>
+          <t>833195</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>843235</t>
+          <t>933759</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1672794</t>
+          <t>1890161</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1456891</t>
+          <t>1808856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1803512</t>
+          <t>1967680</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2552177</t>
+          <t>2521004</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2462346</t>
+          <t>2460119</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2756369</t>
+          <t>2583832</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2886300</t>
+          <t>2844420</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2813060</t>
+          <t>2794219</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3020270</t>
+          <t>2894783</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5438477</t>
+          <t>5365424</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5307759</t>
+          <t>5287905</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5654380</t>
+          <t>5446729</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
